--- a/artfynd/A 60133-2025 artfynd.xlsx
+++ b/artfynd/A 60133-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>65409590</v>
+        <v>121152254</v>
       </c>
       <c r="B2" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,13 +714,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>743553.0530814541</v>
+        <v>743777</v>
       </c>
       <c r="R2" t="n">
-        <v>7305875.200934875</v>
+        <v>7305470</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-08-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-08-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -799,12 +784,7 @@
         <v>65409592</v>
       </c>
       <c r="B3" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -840,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>743684.1383540954</v>
+        <v>743684</v>
       </c>
       <c r="R3" t="n">
-        <v>7305708.134712799</v>
+        <v>7305708</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -873,19 +853,9 @@
           <t>2015-08-17</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2015-08-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -917,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128339785</v>
+        <v>65409588</v>
       </c>
       <c r="B4" t="n">
-        <v>78881</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -956,13 +926,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>743751</v>
+        <v>743726</v>
       </c>
       <c r="R4" t="n">
-        <v>7305587</v>
+        <v>7305768</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2015-08-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2015-08-17</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1020,6 +990,218 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>65409590</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Grundvattnet, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>743553</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7305875</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2015-08-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2015-08-17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128339785</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Grundvattnet, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>743751</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7305587</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
